--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6586-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6586-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26FB38F6-E35F-4D20-82CC-99AFDC216672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0510D2B2-CC3A-4459-9BBB-6A5404048738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{92A9F157-72F5-4AB9-84F6-1345333CD19E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{72964E6A-1059-435B-BC6E-7371F0A884D1}"/>
   </bookViews>
   <sheets>
     <sheet name="6586-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1496,16 +1496,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B18A51D-FDBE-48B8-8950-C6ED4BFD3F32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD666EB0-DDFB-4ABE-931F-42E1F88FE02C}">
   <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="17" width="8.109375" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="2" width="6.625" customWidth="1"/>
+    <col min="3" max="17" width="10.125" customWidth="1"/>
+    <col min="18" max="18" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1533,7 +1533,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1563,7 +1563,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1659,7 +1659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2021</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2020</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2019</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2018</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2017</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39" t="s">
         <v>51</v>
       </c>
